--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135917159</v>
+        <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>96554</v>
+        <v>92384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klärke, Mpd</t>
+          <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591383</v>
+        <v>591478</v>
       </c>
       <c r="R3" t="n">
-        <v>6956781</v>
+        <v>6956688</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,16 +878,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917159</t>
+          <t>https://artportalen.se/Sighting/136969394</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135917154</v>
+        <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>58167</v>
+        <v>92384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klärke, Mpd</t>
+          <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591395</v>
+        <v>591495</v>
       </c>
       <c r="R4" t="n">
-        <v>6956789</v>
+        <v>6956706</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,54 +980,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917154</t>
+          <t>https://artportalen.se/Sighting/136969448</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135917155</v>
+        <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>101454</v>
+        <v>92384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klärke, Mpd</t>
+          <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591390</v>
+        <v>591504</v>
       </c>
       <c r="R5" t="n">
-        <v>6956790</v>
+        <v>6956698</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,54 +1082,54 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917155</t>
+          <t>https://artportalen.se/Sighting/136969656</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135917158</v>
+        <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>99619</v>
+        <v>92384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222812</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klärke, Mpd</t>
+          <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591383</v>
+        <v>591496</v>
       </c>
       <c r="R6" t="n">
-        <v>6956782</v>
+        <v>6956725</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,54 +1184,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917158</t>
+          <t>https://artportalen.se/Sighting/136969754</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135917157</v>
+        <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>99148</v>
+        <v>92384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223049</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Klärke, Mpd</t>
+          <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591392</v>
+        <v>591500</v>
       </c>
       <c r="R7" t="n">
-        <v>6956793</v>
+        <v>6956736</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,6 +1285,1439 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136969961</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136971599</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92384</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>591358</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6956813</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136971599</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136969855</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92113</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>591515</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6956728</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136969855</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135917159</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96554</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>591383</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6956781</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917159</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136971847</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96565</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>591380</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6956787</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136971847</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135917154</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>591395</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6956789</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917154</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136972058</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>591356</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6956752</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136972058</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136970626</v>
+      </c>
+      <c r="B14" t="n">
+        <v>108378</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>591346</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6956867</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136970626</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136969321</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111332</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>591431</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6956694</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136969321</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136970098</v>
+      </c>
+      <c r="B16" t="n">
+        <v>111332</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>591481</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6956823</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136970098</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135917155</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>591390</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6956790</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917155</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136970213</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101465</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>591480</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6956850</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136970213</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136971762</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101465</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>591393</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6956791</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136971762</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135917158</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99619</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>591383</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6956782</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917158</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135917157</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99148</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>591392</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6956793</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135917157</t>
         </is>
@@ -1298,6 +2731,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136969855</v>
+        <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92113</v>
+        <v>92384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591515</v>
+        <v>591470</v>
       </c>
       <c r="R9" t="n">
-        <v>6956728</v>
+        <v>6956725</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,54 +1490,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969855</t>
+          <t>https://artportalen.se/Sighting/136987635</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135917159</v>
+        <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>96554</v>
+        <v>92113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Klärke, Mpd</t>
+          <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591383</v>
+        <v>591515</v>
       </c>
       <c r="R10" t="n">
-        <v>6956781</v>
+        <v>6956728</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,38 +1592,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917159</t>
+          <t>https://artportalen.se/Sighting/136969855</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136971847</v>
+        <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>96565</v>
+        <v>92946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2812</v>
+        <v>2014</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591380</v>
+        <v>591394</v>
       </c>
       <c r="R11" t="n">
-        <v>6956787</v>
+        <v>6956766</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,12 +1663,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På grov björklåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,38 +1699,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136971847</t>
+          <t>https://artportalen.se/Sighting/136986169</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135917154</v>
+        <v>135917159</v>
       </c>
       <c r="B12" t="n">
-        <v>58167</v>
+        <v>96554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591395</v>
+        <v>591383</v>
       </c>
       <c r="R12" t="n">
-        <v>6956789</v>
+        <v>6956781</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1796,16 +1801,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917154</t>
+          <t>https://artportalen.se/Sighting/135917159</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136972058</v>
+        <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>8452</v>
+        <v>96565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591356</v>
+        <v>591380</v>
       </c>
       <c r="R13" t="n">
-        <v>6956752</v>
+        <v>6956787</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,11 +1880,6 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1903,16 +1903,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136972058</t>
+          <t>https://artportalen.se/Sighting/136971847</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136970626</v>
+        <v>136985779</v>
       </c>
       <c r="B14" t="n">
-        <v>108378</v>
+        <v>58000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220083</v>
+        <v>100110</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591346</v>
+        <v>591376</v>
       </c>
       <c r="R14" t="n">
-        <v>6956867</v>
+        <v>6956752</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,51 +2005,56 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970626</t>
+          <t>https://artportalen.se/Sighting/136985779</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136969321</v>
+        <v>136971259</v>
       </c>
       <c r="B15" t="n">
-        <v>111332</v>
+        <v>12377</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220240</v>
+        <v>101283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591431</v>
+        <v>591342</v>
       </c>
       <c r="R15" t="n">
-        <v>6956694</v>
+        <v>6956822</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,12 +2089,18 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Kläckhål i liggande grov björklåga med levande fnösktickor. Kläckhålet något större (uppåt 5 mm) än det vanliga måttet, men sannolikt djupsvart brunbagge. Björkrik trakt runt Klärke med inslag av mycket grova björkhögstubbar.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2107,38 +2118,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969321</t>
+          <t>https://artportalen.se/Sighting/136971259</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136970098</v>
+        <v>136989385</v>
       </c>
       <c r="B16" t="n">
-        <v>111332</v>
+        <v>12377</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220240</v>
+        <v>101283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>591481</v>
+        <v>591371</v>
       </c>
       <c r="R16" t="n">
-        <v>6956823</v>
+        <v>6956760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,12 +2189,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kläckhål i grov björklåga med levande fnösktickor.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2209,16 +2225,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970098</t>
+          <t>https://artportalen.se/Sighting/136989385</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135917155</v>
+        <v>136986308</v>
       </c>
       <c r="B17" t="n">
-        <v>101454</v>
+        <v>44210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,37 +2242,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>101735</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Klärke, Mpd</t>
+          <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591390</v>
+        <v>591416</v>
       </c>
       <c r="R17" t="n">
-        <v>6956790</v>
+        <v>6956786</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2280,12 +2296,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2311,54 +2332,54 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917155</t>
+          <t>https://artportalen.se/Sighting/136986308</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136970213</v>
+        <v>135917154</v>
       </c>
       <c r="B18" t="n">
-        <v>101465</v>
+        <v>58167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Klärke, Klärke, Mpd</t>
+          <t>Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591480</v>
+        <v>591395</v>
       </c>
       <c r="R18" t="n">
-        <v>6956850</v>
+        <v>6956789</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2382,12 +2403,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2413,54 +2434,59 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136970213</t>
+          <t>https://artportalen.se/Sighting/135917154</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136971762</v>
+        <v>136986177</v>
       </c>
       <c r="B19" t="n">
-        <v>101465</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591393</v>
+        <v>591394</v>
       </c>
       <c r="R19" t="n">
-        <v>6956791</v>
+        <v>6956772</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2484,12 +2510,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2515,51 +2541,56 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136971762</t>
+          <t>https://artportalen.se/Sighting/136986177</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135917158</v>
+        <v>136987195</v>
       </c>
       <c r="B20" t="n">
-        <v>99619</v>
+        <v>58169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222812</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Klärke, Mpd</t>
+          <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591383</v>
+        <v>591464</v>
       </c>
       <c r="R20" t="n">
-        <v>6956782</v>
+        <v>6956734</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2586,12 +2617,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2617,51 +2648,55 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917158</t>
+          <t>https://artportalen.se/Sighting/136987195</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135917157</v>
+        <v>136988221</v>
       </c>
       <c r="B21" t="n">
-        <v>99148</v>
+        <v>58169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223049</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Klärke, Mpd</t>
+          <t>Klärke, Klärke, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591392</v>
+        <v>591399</v>
       </c>
       <c r="R21" t="n">
-        <v>6956793</v>
+        <v>6956785</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2688,12 +2723,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2719,7 +2754,1032 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136988221</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136972058</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>591356</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6956752</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136972058</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136970626</v>
+      </c>
+      <c r="B23" t="n">
+        <v>108378</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>591346</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6956867</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136970626</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136969321</v>
+      </c>
+      <c r="B24" t="n">
+        <v>111332</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>591431</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6956694</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136969321</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136970098</v>
+      </c>
+      <c r="B25" t="n">
+        <v>111332</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>591481</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6956823</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136970098</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135917155</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>591390</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6956790</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917155</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136970213</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101465</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>591480</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6956850</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136970213</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136971762</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101465</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>591393</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6956791</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136971762</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135917158</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99619</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>591383</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6956782</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917158</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135917157</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99148</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>591392</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6956793</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135917157</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136987379</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92505</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Klärke, Klärke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>591474</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6956710</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136987379</t>
         </is>
       </c>
     </row>
@@ -2745,6 +3805,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -2153,6 +2153,11 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Klärke, Klärke, Mpd</t>
@@ -2199,7 +2204,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Kläckhål i grov björklåga med levande fnösktickor.</t>
+          <t>Kläckhål i grov björklåga med levande fnösktickor. Kläckhålet något större (uppåt 5 mm) än det vanliga måttet, men sannolikt djupsvart brunbagge.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2208,6 +2213,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92946</v>
+        <v>92948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92505</v>
+        <v>92507</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92948</v>
+        <v>92950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92507</v>
+        <v>92509</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92950</v>
+        <v>92951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92951</v>
+        <v>92957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92510</v>
+        <v>92516</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92957</v>
+        <v>92961</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92516</v>
+        <v>92520</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92961</v>
+        <v>92963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92963</v>
+        <v>92976</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>136985779</v>
       </c>
       <c r="B14" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136986308</v>
       </c>
       <c r="B17" t="n">
-        <v>44210</v>
+        <v>44223</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>136986177</v>
       </c>
       <c r="B19" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>136987195</v>
       </c>
       <c r="B20" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136988221</v>
       </c>
       <c r="B21" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92522</v>
+        <v>92535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92976</v>
+        <v>92978</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>136985779</v>
       </c>
       <c r="B14" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136971259</v>
       </c>
       <c r="B15" t="n">
-        <v>12377</v>
+        <v>12379</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>136989385</v>
       </c>
       <c r="B16" t="n">
-        <v>12377</v>
+        <v>12379</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136986308</v>
       </c>
       <c r="B17" t="n">
-        <v>44223</v>
+        <v>44225</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>136986177</v>
       </c>
       <c r="B19" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>136987195</v>
       </c>
       <c r="B20" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136988221</v>
       </c>
       <c r="B21" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>136972058</v>
       </c>
       <c r="B22" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92535</v>
+        <v>92537</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -2475,11 +2475,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klärke, Klärke, Mpd</t>
@@ -2582,11 +2578,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Klärke, Klärke, Mpd</t>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92978</v>
+        <v>92981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92537</v>
+        <v>92540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92981</v>
+        <v>92991</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>136985779</v>
       </c>
       <c r="B14" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136971259</v>
       </c>
       <c r="B15" t="n">
-        <v>12379</v>
+        <v>12385</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>136989385</v>
       </c>
       <c r="B16" t="n">
-        <v>12379</v>
+        <v>12385</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136986308</v>
       </c>
       <c r="B17" t="n">
-        <v>44225</v>
+        <v>44235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>136986177</v>
       </c>
       <c r="B19" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136987195</v>
       </c>
       <c r="B20" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136988221</v>
       </c>
       <c r="B21" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136972058</v>
       </c>
       <c r="B22" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101506</v>
+        <v>101521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101506</v>
+        <v>101521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92540</v>
+        <v>92550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92991</v>
+        <v>92992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92992</v>
+        <v>92995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>136985779</v>
       </c>
       <c r="B14" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136986308</v>
       </c>
       <c r="B17" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>136986177</v>
       </c>
       <c r="B19" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136987195</v>
       </c>
       <c r="B20" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136988221</v>
       </c>
       <c r="B21" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101522</v>
+        <v>101527</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101522</v>
+        <v>101527</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92551</v>
+        <v>92554</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92995</v>
+        <v>92997</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101527</v>
+        <v>101530</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101527</v>
+        <v>101530</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>92997</v>
+        <v>93003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>136985779</v>
       </c>
       <c r="B14" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>136986177</v>
       </c>
       <c r="B19" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136987195</v>
       </c>
       <c r="B20" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136988221</v>
       </c>
       <c r="B21" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92556</v>
+        <v>92561</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>93003</v>
+        <v>93015</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92561</v>
+        <v>92573</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92573</v>
+        <v>92574</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>93016</v>
+        <v>93019</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92574</v>
+        <v>92577</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>93019</v>
+        <v>93020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96646</v>
+        <v>96647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108474</v>
+        <v>108476</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101552</v>
+        <v>101553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101552</v>
+        <v>101553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969394</v>
       </c>
       <c r="B3" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136969448</v>
       </c>
       <c r="B4" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136969656</v>
       </c>
       <c r="B5" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136969754</v>
       </c>
       <c r="B6" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136969961</v>
       </c>
       <c r="B7" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136971599</v>
       </c>
       <c r="B8" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136987635</v>
       </c>
       <c r="B9" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136969855</v>
       </c>
       <c r="B10" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136986169</v>
       </c>
       <c r="B11" t="n">
-        <v>93020</v>
+        <v>93023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136971847</v>
       </c>
       <c r="B13" t="n">
-        <v>96647</v>
+        <v>96650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>136985779</v>
       </c>
       <c r="B14" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>136986177</v>
       </c>
       <c r="B19" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136987195</v>
       </c>
       <c r="B20" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>136988221</v>
       </c>
       <c r="B21" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136970626</v>
       </c>
       <c r="B23" t="n">
-        <v>108476</v>
+        <v>108480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136969321</v>
       </c>
       <c r="B24" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136970098</v>
       </c>
       <c r="B25" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>136970213</v>
       </c>
       <c r="B27" t="n">
-        <v>101553</v>
+        <v>101556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136971762</v>
       </c>
       <c r="B28" t="n">
-        <v>101553</v>
+        <v>101556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>136987379</v>
       </c>
       <c r="B31" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
